--- a/WORD/all.xlsx
+++ b/WORD/all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\WORD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843D77C0-B493-4B64-9B34-55683B96A44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0C39D5-ACCC-41BE-AF2B-E9D45467E56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="9375" yWindow="5550" windowWidth="28365" windowHeight="9255" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7.13" sheetId="1" r:id="rId1"/>
@@ -24,13 +24,13 @@
     <sheet name="8.10" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7.13'!$A$1:$E$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'7.14'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'7.17'!$A$1:$F$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'7.18'!$A$1:$F$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'7.19'!$A$1:$E$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'7.20'!$A$1:$E$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'8.9'!$A$1:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7.13'!$A$1:$D$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'7.14'!$A$1:$D$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'7.17'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'7.18'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'7.19'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'7.20'!$A$1:$D$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'8.9'!$A$1:$D$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,13 +46,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="554">
   <si>
     <t>Fre</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rand</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2851,345 +2847,273 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="9" customWidth="1"/>
     <col min="2" max="2" width="24.125" customWidth="1"/>
     <col min="3" max="3" width="19.75" customWidth="1"/>
     <col min="4" max="4" width="27.875" customWidth="1"/>
-    <col min="5" max="5" width="10.75" customWidth="1"/>
-    <col min="6" max="6" width="50.25" customWidth="1"/>
+    <col min="5" max="5" width="50.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="D1" s="29" t="s">
-        <v>552</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="28" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E1" s="28" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="9">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2">
-        <f t="shared" ref="E2:E18" ca="1" si="0">RAND()</f>
-        <v>0.39644205127532528</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A3" s="9">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.72277136177801826</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A4" s="9">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.99093125052616904</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A5" s="9">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5">
-        <f t="shared" ca="1" si="0"/>
-        <v>9.1186715151643449E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A6" s="9">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.269708699447615</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A7" s="9">
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.45426528856428172</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="28.5" x14ac:dyDescent="0.15">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="28.5" x14ac:dyDescent="0.15">
       <c r="A8" s="9">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.60532099764280234</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+        <v>15</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A9" s="9">
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.88915391850371206</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+        <v>39</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A10" s="9">
         <v>1</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.87260914399520206</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="11" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A11" s="9">
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.81809761590454544</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="12" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A12" s="9">
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.85681026618688227</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A13" s="9">
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.31721269783449468</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A14" s="9">
         <v>0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.25660953177118284</v>
-      </c>
-      <c r="F14" s="13"/>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+      <c r="E14" s="13"/>
+    </row>
+    <row r="15" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A15" s="9">
         <v>0</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.87671177092502617</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A16" s="11">
         <v>0</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16">
-        <f t="shared" ca="1" si="0"/>
-        <v>6.7962928449713078E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="17" spans="1:4" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A17" s="9">
         <v>0</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.38674931244516875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="18" spans="1:4" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A18" s="9">
         <v>0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.64053990400831462</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E18" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E18">
+  <autoFilter ref="A1:D18" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D18">
       <sortCondition descending="1" ref="A1:A18"/>
     </sortState>
   </autoFilter>
@@ -3202,7 +3126,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="11.875" customWidth="1"/>
@@ -3210,239 +3134,184 @@
     <col min="4" max="4" width="30.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="D1" s="29" t="s">
-        <v>552</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="29" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="E1" s="29" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="9">
         <v>4</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2">
-        <f t="shared" ref="E2:E14" ca="1" si="0">RAND()</f>
-        <v>0.40803802980087556</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="9">
         <v>4</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.3226658869545358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="9">
         <v>4</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.4333301042384804</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="9">
         <v>2</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.615210053780055</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A6" s="9">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="E6">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.89928371795239381</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="9">
         <v>1</v>
       </c>
       <c r="B7" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="27" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8" s="9">
+        <v>0</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="9">
+        <v>0</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" s="9">
+        <v>0</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E7">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.21522081603718513</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A8" s="9">
-        <v>0</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8">
-        <f t="shared" ca="1" si="0"/>
-        <v>6.7145172924733543E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A9" s="9">
-        <v>0</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.86663671960014532</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A10" s="9">
-        <v>0</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.60784352476688774</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="9">
         <v>0</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="4" t="s">
+    </row>
+    <row r="12" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
+      <c r="A12" s="9">
+        <v>0</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="9">
+        <v>0</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" s="9">
+        <v>0</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="E11">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.36718480625208338</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
-      <c r="A12" s="9">
-        <v>0</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.19373873758063698</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A13" s="9">
-        <v>0</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.73364638834355922</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A14" s="9">
-        <v>0</v>
-      </c>
-      <c r="B14" s="10" t="s">
+      <c r="D14" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.16796519357383577</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E15" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E14">
+  <autoFilter ref="A1:D15" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
       <sortCondition descending="1" ref="A1:A15"/>
     </sortState>
   </autoFilter>
@@ -3455,457 +3324,362 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="2" width="11.375" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="24.375" customWidth="1"/>
-    <col min="6" max="6" width="19.375" customWidth="1"/>
+    <col min="5" max="5" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="D1" s="29" t="s">
-        <v>552</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="29" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="E1" s="29" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="9">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2">
-        <f t="shared" ref="E2:E24" ca="1" si="0">RAND()</f>
-        <v>0.12665548932783322</v>
-      </c>
-      <c r="F2" s="27" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="E2" s="27" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="9">
         <v>3</v>
       </c>
       <c r="B3" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ca="1" si="0"/>
-        <v>2.7750893713544889E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="9">
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.5078372973089037</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E5">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.6374656877953323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="9">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E6">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.82337209672528566</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="E6" s="27" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="9">
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.33486671727557826</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="9">
         <v>3</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E8">
-        <f t="shared" ca="1" si="0"/>
-        <v>4.315109271555484E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="9">
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.27243765394075392</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="9">
         <v>4</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.97817156815462503</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="9">
         <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E11">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.73236721475584399</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="9">
         <v>4</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.66310244447274391</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="9">
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.70889030691025645</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="9">
         <v>2</v>
       </c>
       <c r="B14" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.23856667650334373</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="9">
         <v>2</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="D15" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.14537860871368802</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="9">
         <v>3</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="6" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="9">
+        <v>1</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" s="9">
+        <v>1</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" s="9">
+        <v>1</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" s="9">
+        <v>0</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="19.5" x14ac:dyDescent="0.15">
+      <c r="A21" s="9">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" s="9">
+        <v>0</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E16">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.66984771726379089</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" s="9">
-        <v>1</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E17">
-        <f t="shared" ca="1" si="0"/>
-        <v>8.3832236761873791E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="9">
-        <v>1</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18">
-        <f t="shared" ca="1" si="0"/>
-        <v>9.3967198991928624E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" s="9">
-        <v>1</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.14453156483973195</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" s="9">
-        <v>0</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="E20">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.86908182679382495</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
-      <c r="A21" s="9">
-        <v>0</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="E21">
-        <f t="shared" ca="1" si="0"/>
-        <v>3.6019909918030057E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" s="9">
-        <v>0</v>
-      </c>
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="D22" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.18983834399948574</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="9">
         <v>0</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.2264597291219631</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="9">
         <v>1</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E24">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.82152358526253</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="9">
         <v>0</v>
       </c>
       <c r="B25" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>447</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="D25" s="17" t="s">
         <v>448</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>449</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F25" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:E25" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3915,7 +3689,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
@@ -3924,427 +3698,328 @@
     <col min="4" max="4" width="25.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="D1" s="29" t="s">
+        <v>551</v>
+      </c>
+      <c r="E1" s="31" t="s">
         <v>552</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="9">
         <v>3</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="E2">
-        <f t="shared" ref="E2:E25" ca="1" si="0">RAND()</f>
-        <v>0.65252021212122946</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="9">
         <v>3</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.67662202735387289</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="9">
         <v>4</v>
       </c>
       <c r="B4" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="E4">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.56727829017914433</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="9">
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E5">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.54482087060846218</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="9">
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E6">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.81959674032949403</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="E6" s="12" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="9">
         <v>4</v>
       </c>
       <c r="B7" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="E7">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.75359376480439522</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="9">
         <v>3</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.53586656727491122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="9">
         <v>2</v>
       </c>
       <c r="B9" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.688569328684147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="9">
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="E10">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.30587857987891598</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="9">
         <v>2</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.9442802256958911</v>
-      </c>
-      <c r="F11" s="27" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="E11" s="27" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="9">
         <v>3</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E12">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.6655328345266377</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="9">
         <v>1</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E13">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.60866630968214819</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="9">
         <v>2</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E14">
-        <f t="shared" ca="1" si="0"/>
-        <v>4.996140403130811E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="9">
         <v>1</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D15" s="6" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="9">
+        <v>1</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="9">
+        <v>1</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" s="9">
+        <v>1</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" s="9">
+        <v>1</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" s="9">
+        <v>1</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" s="9">
+        <v>1</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" s="9">
+        <v>0</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" s="9">
+        <v>0</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E15">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.20655137872069385</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A16" s="9">
-        <v>1</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E16">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.49302443128339191</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" s="9">
-        <v>1</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E17">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.43683788008997604</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="9">
-        <v>1</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="E18">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.22349825264137746</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" s="9">
-        <v>1</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="D23" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" s="9">
+        <v>0</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.25008202646179378</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" s="9">
-        <v>1</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E20">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.2245166566065333</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21" s="9">
-        <v>1</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E21">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.68435794712519471</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" s="9">
-        <v>0</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="E22">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.7878840815705338</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23" s="9">
-        <v>0</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="E23">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.3021002783808906</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24" s="9">
-        <v>0</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E24">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.43649777011397339</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="25" spans="1:4" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A25" s="9">
         <v>0</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E25">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.28131424148604889</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F25" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:E25" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4352,7 +4027,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
@@ -4361,423 +4036,328 @@
     <col min="4" max="4" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>14</v>
-      </c>
       <c r="D1" s="28" t="s">
-        <v>552</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="32" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+        <v>551</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="9">
         <v>4</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="E2" s="9">
-        <f t="shared" ref="E2:E24" ca="1" si="0">RAND()</f>
-        <v>0.56921534603686408</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="9">
         <v>3</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="E3" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.79752513501155486</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="E4" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.35783817913957794</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="E5" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.69387381779845436</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="9">
         <v>4</v>
       </c>
       <c r="B6" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="D6" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>242</v>
-      </c>
-      <c r="E6" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.23422816665115764</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="9">
         <v>4</v>
       </c>
       <c r="B7" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="D7" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="E7" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.91891114305417432</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="9">
         <v>4</v>
       </c>
       <c r="B8" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="D8" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="E8" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.83715272522293049</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="9">
         <v>3</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="E9" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.70915764886593768</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="9">
         <v>2</v>
       </c>
       <c r="B10" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="D10" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="E10" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.72413992974467944</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="19.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="11" spans="1:5" ht="19.5" x14ac:dyDescent="0.15">
       <c r="A11" s="9">
         <v>2</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="E11" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>7.0178595518838871E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="9">
         <v>3</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="E12" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.48160931255848127</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="9">
         <v>1</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="E13" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.53617265393639324</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="9">
         <v>1</v>
       </c>
       <c r="B14" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="C14" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="D14" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="E14" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.23176960353884468</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="9">
         <v>2</v>
       </c>
       <c r="B15" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="D15" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="E15" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.32894332093486278</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="9">
         <v>1</v>
       </c>
       <c r="B16" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="D16" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="E16" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.96008064130832049</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="9">
         <v>1</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="23" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" s="9">
+        <v>1</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" s="9">
+        <v>0</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" s="9">
+        <v>0</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" s="9">
+        <v>0</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" s="9">
+        <v>0</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" s="9">
+        <v>0</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" s="9">
+        <v>0</v>
+      </c>
+      <c r="B24" s="23" t="s">
         <v>250</v>
-      </c>
-      <c r="E17" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.83999380309302107</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="9">
-        <v>1</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="E18" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.64063635906067606</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" s="9">
-        <v>0</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="E19" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.85156276814802123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" s="9">
-        <v>0</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="E20" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.10931007713310514</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21" s="9">
-        <v>0</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="E21" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.37353610253463321</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" s="9">
-        <v>0</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="E22" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.17395206401684737</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23" s="9">
-        <v>0</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="E23" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.46839334784174114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24" s="9">
-        <v>0</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>251</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="E24" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.98228324684899337</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E24" xr:uid="{00000000-0009-0000-0000-000004000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E24">
+  <autoFilter ref="A1:D24" xr:uid="{00000000-0009-0000-0000-000004000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D24">
       <sortCondition descending="1" ref="A1:A24"/>
     </sortState>
   </autoFilter>
@@ -4789,7 +4369,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
@@ -4798,869 +4378,646 @@
     <col min="4" max="4" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="D1" s="29" t="s">
-        <v>552</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+        <v>551</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="9">
         <v>2</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>270</v>
-      </c>
       <c r="D2" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="E2">
-        <f t="shared" ref="E2:E33" ca="1" si="0">RAND()</f>
-        <v>0.66901381870305809</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.53290663721997711</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="9">
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E4">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.40307061536336364</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="9">
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="E5">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.67584519864467607</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="9">
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="E6">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.99731744673096501</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="9">
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="E7">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.98069488564264495</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="9">
         <v>2</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>334</v>
-      </c>
       <c r="D8" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="E8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.5639108933967103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="9">
         <v>1</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="E9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.67339691737999807</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="9">
         <v>2</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>325</v>
-      </c>
-      <c r="E10">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.61971320465454427</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="9">
         <v>2</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" s="9">
+        <v>1</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="9">
+        <v>1</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="E11">
-        <f t="shared" ca="1" si="0"/>
-        <v>1.281763640497191E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A12" s="9">
-        <v>1</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="E12">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.67852732235140145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A13" s="9">
-        <v>1</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="E13">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.22691099780469925</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="9">
         <v>2</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="E14">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.35128001866565295</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="9">
         <v>2</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.48712464787914278</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="9">
         <v>2</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="E16">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.6264711003492045</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="9">
         <v>1</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="E17">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.34423164582362897</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="9">
         <v>2</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="E18">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.40841081397466705</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="9">
         <v>2</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="E19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.60154762834024234</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="9">
         <v>2</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="E20">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.90230060144125912</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="9">
         <v>1</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="E21">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.68258082904312278</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="9">
         <v>1</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="E22">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.39042626844308226</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="9">
         <v>1</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="E23">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.7718467638707196</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="9">
         <v>2</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="E24">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.70622848666955873</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="9">
         <v>1</v>
       </c>
       <c r="B25" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A26" s="9">
+        <v>1</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A27" s="9">
+        <v>0</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A28" s="9">
+        <v>0</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A29" s="9">
+        <v>0</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A30" s="9">
+        <v>0</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A31" s="9">
+        <v>0</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A32" s="9">
+        <v>0</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A33" s="9">
+        <v>0</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A34" s="9">
+        <v>0</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A35" s="9">
+        <v>0</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A36" s="9">
+        <v>1</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A37" s="9">
+        <v>0</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A38" s="9">
+        <v>0</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A39" s="9">
+        <v>0</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A40" s="9">
+        <v>0</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A41" s="9">
+        <v>0</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A42" s="9">
+        <v>0</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A43" s="9">
+        <v>0</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A44" s="9">
+        <v>0</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A45" s="9">
+        <v>0</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A46" s="9">
+        <v>0</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A47" s="9">
+        <v>0</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="E25">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.64644877221141361</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26" s="9">
-        <v>1</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="E26">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.22050103368195884</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27" s="9">
-        <v>0</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="E27">
-        <f t="shared" ca="1" si="0"/>
-        <v>3.509916471296326E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28" s="9">
-        <v>0</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="E28">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.97656539805344134</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29" s="9">
-        <v>0</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="E29">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.95551173673618739</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30" s="9">
-        <v>0</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="E30">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.3505179238261783</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A31" s="9">
-        <v>0</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="E31">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.18301639262851088</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A32" s="9">
-        <v>0</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="E32">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.47310598569847284</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A33" s="9">
-        <v>0</v>
-      </c>
-      <c r="B33" s="7" t="s">
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A48" s="9">
+        <v>0</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A49" s="9">
+        <v>0</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A50" s="9">
+        <v>0</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A51" s="9">
+        <v>0</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A52" s="9">
+        <v>1</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="C52" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="E33">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.11985519745094186</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A34" s="9">
-        <v>0</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="E34">
-        <f t="shared" ref="E34:E56" ca="1" si="1">RAND()</f>
-        <v>0.93933689426465528</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A35" s="9">
-        <v>0</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="E35">
-        <f t="shared" ca="1" si="1"/>
-        <v>5.0924159882415276E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A36" s="9">
-        <v>1</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="E36">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.37843563445479678</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A37" s="9">
-        <v>0</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="E37">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.91562006838196175</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A38" s="9">
-        <v>0</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="E38">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.11018219501840165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A39" s="9">
-        <v>0</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="E39">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.9329431354288612</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A40" s="9">
-        <v>0</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="E40">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.27506108424751086</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A41" s="9">
-        <v>0</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="E41">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.94569741534296736</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A42" s="9">
-        <v>0</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="E42">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.47488885267600944</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="9">
-        <v>0</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="E43">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.23022591886134736</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="9">
-        <v>0</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="E44">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.6971349388113963E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="9">
-        <v>0</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="E45">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.69913853089619038</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="9">
-        <v>0</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="E46">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.75393732380060174</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="9">
-        <v>0</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="E47">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.58099610530460222</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="9">
-        <v>0</v>
-      </c>
-      <c r="B48" s="7" t="s">
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A53" s="9">
+        <v>0</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C53" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="C48" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="E48">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.51234526042673489</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="9">
-        <v>0</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="E49">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.29715038499126312</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="9">
-        <v>0</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="E50">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.21658433635391339</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="9">
-        <v>0</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="E51">
-        <f t="shared" ca="1" si="1"/>
-        <v>6.3975544913314919E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="9">
-        <v>1</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="E52">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.59289122818283579</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A53" s="9">
-        <v>0</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="E53">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.99723688406241462</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54" s="9">
         <v>2</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="E54">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.82979634630788768</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55" s="9">
         <v>0</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="E55">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.96730411141928518</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56" s="9">
         <v>0</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="E56">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.71868203866469926</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E56" xr:uid="{00000000-0009-0000-0000-000005000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E56">
+  <autoFilter ref="A1:D56" xr:uid="{00000000-0009-0000-0000-000005000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D56">
       <sortCondition descending="1" ref="A1:A56"/>
     </sortState>
   </autoFilter>
@@ -5672,484 +5029,373 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="3" width="13.25" customWidth="1"/>
     <col min="4" max="4" width="29.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>14</v>
-      </c>
       <c r="D1" s="28" t="s">
-        <v>552</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="32" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+        <v>551</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>380</v>
       </c>
-      <c r="D2" s="14" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="9">
+        <v>0</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>381</v>
       </c>
-      <c r="E2">
-        <f t="shared" ref="E2:E28" ca="1" si="0">RAND()</f>
-        <v>0.92425224216084523</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A3" s="9">
-        <v>0</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="D3" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="D3" s="14" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="9">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>383</v>
       </c>
-      <c r="E3">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.77195308033798926</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="9">
-        <v>1</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="D4" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="D4" s="14" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="9">
+        <v>1</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>385</v>
       </c>
-      <c r="E4">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.39359690875753173</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A5" s="9">
-        <v>1</v>
-      </c>
-      <c r="B5" s="18" t="s">
+      <c r="C5" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>387</v>
       </c>
-      <c r="D5" s="14" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="9">
+        <v>0</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>388</v>
       </c>
-      <c r="E5">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.87844347233923192</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A6" s="9">
-        <v>0</v>
-      </c>
-      <c r="B6" s="18" t="s">
+      <c r="C6" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D6" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="D6" s="14" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7" s="9">
+        <v>0</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>391</v>
       </c>
-      <c r="E6">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.74723620672396285</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A7" s="9">
-        <v>0</v>
-      </c>
-      <c r="B7" s="18" t="s">
+      <c r="D7" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="D7" s="14" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8" s="9">
+        <v>0</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>393</v>
       </c>
-      <c r="E7">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.52657723156861269</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A8" s="9">
-        <v>0</v>
-      </c>
-      <c r="B8" s="18" t="s">
+      <c r="C8" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="C8" s="14" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="9">
+        <v>0</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>395</v>
-      </c>
-      <c r="E8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.63271414560060169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A9" s="9">
-        <v>0</v>
-      </c>
-      <c r="B9" s="14" t="s">
+      <c r="C9" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="D9" s="14" t="s">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" s="9">
+        <v>0</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>399</v>
       </c>
-      <c r="E9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.54008879676878807</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A10" s="9">
-        <v>0</v>
-      </c>
-      <c r="B10" s="16" t="s">
+      <c r="C10" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="D10" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="D10" s="14" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11" s="9">
+        <v>0</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="E10">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.81754504367693281</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A11" s="9">
-        <v>0</v>
-      </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="D11" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="D11" s="14" t="s">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" s="9">
+        <v>0</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>405</v>
       </c>
-      <c r="E11">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.35095056082799303</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A12" s="9">
-        <v>0</v>
-      </c>
-      <c r="B12" s="16" t="s">
+      <c r="C12" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>401</v>
-      </c>
-      <c r="D12" s="14" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="9">
+        <v>1</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>407</v>
       </c>
-      <c r="E12">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.96320600807451773</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A13" s="9">
-        <v>1</v>
-      </c>
-      <c r="B13" s="18" t="s">
+      <c r="C13" s="18" t="s">
+        <v>503</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>504</v>
-      </c>
-      <c r="D13" s="14" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" s="9">
+        <v>0</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="E13">
-        <f t="shared" ca="1" si="0"/>
-        <v>3.4727131769981101E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A14" s="9">
-        <v>0</v>
-      </c>
-      <c r="B14" s="16" t="s">
+      <c r="D14" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="D14" s="14" t="s">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="9">
+        <v>0</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="E14">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.54524701802368025</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A15" s="9">
-        <v>0</v>
-      </c>
-      <c r="B15" s="16" t="s">
+      <c r="D15" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="D15" s="14" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="9">
+        <v>1</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>413</v>
       </c>
-      <c r="E15">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.21881806910436186</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A16" s="9">
-        <v>1</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="D16" s="14" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="9">
+        <v>0</v>
+      </c>
+      <c r="B17" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="E16">
-        <f t="shared" ca="1" si="0"/>
-        <v>7.8666556913995267E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" s="9">
-        <v>0</v>
-      </c>
-      <c r="B17" s="16" t="s">
+      <c r="D17" s="14" t="s">
         <v>415</v>
       </c>
-      <c r="D17" s="14" t="s">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" s="9">
+        <v>0</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>416</v>
       </c>
-      <c r="E17">
-        <f t="shared" ca="1" si="0"/>
-        <v>9.9063190168050541E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="9">
-        <v>0</v>
-      </c>
-      <c r="B18" s="16" t="s">
+      <c r="D18" s="14" t="s">
         <v>417</v>
       </c>
-      <c r="D18" s="14" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" s="9">
+        <v>0</v>
+      </c>
+      <c r="B19" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="E18">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.50537300718401068</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" s="9">
-        <v>0</v>
-      </c>
-      <c r="B19" s="14" t="s">
+      <c r="C19" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="C19" s="14" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" s="9">
+        <v>1</v>
+      </c>
+      <c r="B20" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="E19">
-        <f t="shared" ca="1" si="0"/>
-        <v>2.9214250604160052E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" s="9">
-        <v>1</v>
-      </c>
-      <c r="B20" s="14" t="s">
+      <c r="D20" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="D20" s="14" t="s">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" s="9">
+        <v>0</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>423</v>
       </c>
-      <c r="E20">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.45478513894171435</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21" s="9">
-        <v>0</v>
-      </c>
-      <c r="B21" s="16" t="s">
+      <c r="C21" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="D21" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="D21" s="14" t="s">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" s="9">
+        <v>0</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>426</v>
       </c>
-      <c r="E21">
-        <f t="shared" ca="1" si="0"/>
-        <v>4.8943744846575155E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" s="9">
-        <v>0</v>
-      </c>
-      <c r="B22" s="18" t="s">
+      <c r="C22" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="D22" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="C22" s="14" t="s">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" s="9">
+        <v>1</v>
+      </c>
+      <c r="B23" s="18" t="s">
         <v>429</v>
       </c>
-      <c r="D22" s="14" t="s">
-        <v>428</v>
-      </c>
-      <c r="E22">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.90803376464043262</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23" s="9">
-        <v>1</v>
-      </c>
-      <c r="B23" s="18" t="s">
+      <c r="C23" s="14" t="s">
         <v>430</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="D23" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="D23" s="14" t="s">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" s="9">
+        <v>1</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>432</v>
       </c>
-      <c r="E23">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.27202556965896874</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24" s="9">
-        <v>1</v>
-      </c>
-      <c r="B24" s="16" t="s">
+      <c r="C24" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="D24" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="D24" s="14" t="s">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A25" s="9">
+        <v>1</v>
+      </c>
+      <c r="B25" s="16" t="s">
         <v>435</v>
       </c>
-      <c r="E24">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.64882493692953214</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25" s="9">
-        <v>1</v>
-      </c>
-      <c r="B25" s="16" t="s">
+      <c r="C25" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="D25" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="C25" s="14" t="s">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A26" s="9">
+        <v>1</v>
+      </c>
+      <c r="B26" s="16" t="s">
         <v>438</v>
       </c>
-      <c r="D25" s="14" t="s">
-        <v>437</v>
-      </c>
-      <c r="E25">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.81824049359705164</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26" s="9">
-        <v>1</v>
-      </c>
-      <c r="B26" s="16" t="s">
+      <c r="C26" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="D26" s="14" t="s">
         <v>440</v>
       </c>
-      <c r="D26" s="14" t="s">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A27" s="9">
+        <v>0</v>
+      </c>
+      <c r="B27" s="16" t="s">
         <v>441</v>
       </c>
-      <c r="E26">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.15823027242107202</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27" s="9">
-        <v>0</v>
-      </c>
-      <c r="B27" s="16" t="s">
+      <c r="C27" s="14" t="s">
         <v>442</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="D27" s="14" t="s">
         <v>443</v>
       </c>
-      <c r="D27" s="14" t="s">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A28" s="9">
+        <v>1</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>444</v>
       </c>
-      <c r="E27">
-        <f t="shared" ca="1" si="0"/>
-        <v>2.6479181837717469E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28" s="9">
-        <v>1</v>
-      </c>
-      <c r="B28" s="16" t="s">
+      <c r="D28" s="14" t="s">
         <v>445</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>446</v>
-      </c>
-      <c r="E28">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.40951890751539133</v>
       </c>
     </row>
   </sheetData>
@@ -6161,7 +5407,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="19"/>
@@ -6171,397 +5417,302 @@
     <col min="5" max="16384" width="9" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="19" t="s">
-        <v>14</v>
-      </c>
       <c r="D1" s="19" t="s">
-        <v>552</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+        <v>551</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="19">
         <v>1</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>450</v>
+      </c>
+      <c r="D2" s="19" t="s">
         <v>451</v>
       </c>
-      <c r="D2" s="19" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="19">
+        <v>0</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>452</v>
       </c>
-      <c r="E2" s="19">
-        <f ca="1">RAND()</f>
-        <v>8.668274456803271E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A3" s="19">
-        <v>0</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="D3" s="19" t="s">
         <v>453</v>
       </c>
-      <c r="D3" s="19" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="19">
+        <v>1</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>454</v>
       </c>
-      <c r="E3" s="19">
-        <f t="shared" ref="E3:E24" ca="1" si="0">RAND()</f>
-        <v>0.14949642422262011</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="19">
-        <v>1</v>
-      </c>
-      <c r="B4" s="19" t="s">
+      <c r="D4" s="19" t="s">
         <v>455</v>
       </c>
-      <c r="D4" s="19" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="19">
+        <v>0</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>456</v>
       </c>
-      <c r="E4" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>7.8000603855848172E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A5" s="19">
-        <v>0</v>
-      </c>
-      <c r="B5" s="19" t="s">
+      <c r="D5" s="19" t="s">
         <v>457</v>
       </c>
-      <c r="D5" s="19" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="19">
+        <v>1</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>458</v>
       </c>
-      <c r="E5" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.20103389444157527</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A6" s="19">
-        <v>1</v>
-      </c>
-      <c r="B6" s="19" t="s">
+      <c r="D6" s="19" t="s">
         <v>459</v>
       </c>
-      <c r="D6" s="19" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7" s="19">
+        <v>0</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>460</v>
       </c>
-      <c r="E6" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.7845380414505283</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A7" s="19">
-        <v>0</v>
-      </c>
-      <c r="B7" s="19" t="s">
+      <c r="C7" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>461</v>
       </c>
-      <c r="C7" s="19" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8" s="19">
+        <v>0</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>463</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>462</v>
-      </c>
-      <c r="E7" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.81312429374869855</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A8" s="19">
-        <v>0</v>
-      </c>
-      <c r="B8" s="19" t="s">
+      <c r="C8" s="19" t="s">
         <v>464</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="D8" s="19" t="s">
         <v>465</v>
       </c>
-      <c r="D8" s="19" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="19">
+        <v>1</v>
+      </c>
+      <c r="B9" s="19" t="s">
         <v>466</v>
       </c>
-      <c r="E8" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.91285861375434685</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A9" s="19">
-        <v>1</v>
-      </c>
-      <c r="B9" s="19" t="s">
+      <c r="D9" s="19" t="s">
         <v>467</v>
       </c>
-      <c r="D9" s="19" t="s">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" s="19">
+        <v>1</v>
+      </c>
+      <c r="B10" s="19" t="s">
         <v>468</v>
       </c>
-      <c r="E9" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.32971661402541852</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A10" s="19">
-        <v>1</v>
-      </c>
-      <c r="B10" s="19" t="s">
+      <c r="C10" s="19" t="s">
         <v>469</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="D10" s="19" t="s">
         <v>470</v>
       </c>
-      <c r="D10" s="19" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11" s="19">
+        <v>0</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>471</v>
       </c>
-      <c r="E10" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.38071147921960136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A11" s="19">
-        <v>0</v>
-      </c>
-      <c r="B11" s="19" t="s">
+      <c r="C11" s="19" t="s">
         <v>472</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="D11" s="19" t="s">
         <v>473</v>
       </c>
-      <c r="D11" s="19" t="s">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" s="19">
+        <v>0</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>474</v>
       </c>
-      <c r="E11" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.76969411037562074</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A12" s="19">
-        <v>0</v>
-      </c>
-      <c r="B12" s="19" t="s">
+      <c r="C12" s="19" t="s">
         <v>475</v>
       </c>
-      <c r="C12" s="19" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="19">
+        <v>1</v>
+      </c>
+      <c r="B13" s="19" t="s">
         <v>476</v>
       </c>
-      <c r="E12" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.85388860639279063</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A13" s="19">
-        <v>1</v>
-      </c>
-      <c r="B13" s="19" t="s">
+      <c r="D13" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="D13" s="19" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" s="19">
+        <v>0</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="E13" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.11244344211573143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A14" s="19">
-        <v>0</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="C14" s="19" t="s">
+      <c r="D14" s="19" t="s">
         <v>479</v>
       </c>
-      <c r="D14" s="19" t="s">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="19">
+        <v>1</v>
+      </c>
+      <c r="B15" s="19" t="s">
         <v>480</v>
       </c>
-      <c r="E14" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.61792462226817457</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A15" s="19">
-        <v>1</v>
-      </c>
-      <c r="B15" s="19" t="s">
+      <c r="C15" s="19" t="s">
         <v>481</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="D15" s="19" t="s">
         <v>482</v>
       </c>
-      <c r="D15" s="19" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="19">
+        <v>1</v>
+      </c>
+      <c r="B16" s="19" t="s">
         <v>483</v>
       </c>
-      <c r="E15" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.76686838361282317</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A16" s="19">
-        <v>1</v>
-      </c>
-      <c r="B16" s="19" t="s">
+      <c r="D16" s="19" t="s">
         <v>484</v>
       </c>
-      <c r="D16" s="19" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="19">
+        <v>1</v>
+      </c>
+      <c r="B17" s="19" t="s">
         <v>485</v>
       </c>
-      <c r="E16" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>2.6663464355392019E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" s="19">
-        <v>1</v>
-      </c>
-      <c r="B17" s="19" t="s">
+      <c r="D17" s="19" t="s">
         <v>486</v>
       </c>
-      <c r="D17" s="19" t="s">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" s="19">
+        <v>1</v>
+      </c>
+      <c r="B18" s="19" t="s">
         <v>487</v>
       </c>
-      <c r="E17" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.45420161457375197</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="19">
-        <v>1</v>
-      </c>
-      <c r="B18" s="19" t="s">
+      <c r="D18" s="19" t="s">
         <v>488</v>
       </c>
-      <c r="D18" s="19" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" s="19">
+        <v>1</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>489</v>
       </c>
-      <c r="E18" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>4.1157169097658652E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" s="19">
-        <v>1</v>
-      </c>
-      <c r="B19" s="19" t="s">
+      <c r="D19" s="19" t="s">
         <v>491</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="D19" s="19" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" s="19">
+        <v>0</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>492</v>
       </c>
-      <c r="E19" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.83655576344856319</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" s="19">
-        <v>0</v>
-      </c>
-      <c r="B20" s="19" t="s">
+      <c r="D20" s="19" t="s">
         <v>493</v>
       </c>
-      <c r="D20" s="19" t="s">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" s="19">
+        <v>0</v>
+      </c>
+      <c r="B21" s="19" t="s">
         <v>494</v>
       </c>
-      <c r="E20" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.92900152357313615</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21" s="19">
-        <v>0</v>
-      </c>
-      <c r="B21" s="19" t="s">
+      <c r="D21" s="19" t="s">
         <v>495</v>
       </c>
-      <c r="D21" s="19" t="s">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" s="19">
+        <v>0</v>
+      </c>
+      <c r="B22" s="19" t="s">
         <v>496</v>
       </c>
-      <c r="E21" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.92693665293877259</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" s="19">
-        <v>0</v>
-      </c>
-      <c r="B22" s="19" t="s">
+      <c r="D22" s="19" t="s">
         <v>497</v>
       </c>
-      <c r="D22" s="19" t="s">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" s="19">
+        <v>1</v>
+      </c>
+      <c r="B23" s="19" t="s">
         <v>498</v>
       </c>
-      <c r="E22" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.10690580157998442</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23" s="19">
-        <v>1</v>
-      </c>
-      <c r="B23" s="19" t="s">
+      <c r="C23" s="19" t="s">
         <v>499</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="D23" s="19" t="s">
         <v>500</v>
       </c>
-      <c r="D23" s="19" t="s">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" s="19">
+        <v>1</v>
+      </c>
+      <c r="B24" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="E23" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.26167092735306563</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24" s="19">
-        <v>1</v>
-      </c>
-      <c r="B24" s="19" t="s">
+      <c r="D24" s="19" t="s">
         <v>502</v>
       </c>
-      <c r="D24" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="E24" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>4.3854247979873584E-2</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E24" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <autoFilter ref="A1:D24" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6570,344 +5721,264 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="2" width="16.75" style="9" customWidth="1"/>
     <col min="3" max="3" width="16.25" style="9" customWidth="1"/>
     <col min="4" max="4" width="26.625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="6.75" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="9"/>
+    <col min="5" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="19" t="s">
-        <v>14</v>
-      </c>
       <c r="D1" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+        <v>551</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="9">
         <v>0</v>
       </c>
       <c r="B2" s="20" t="s">
+        <v>504</v>
+      </c>
+      <c r="D2" s="20" t="s">
         <v>505</v>
       </c>
-      <c r="D2" s="20" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="9">
+        <v>1</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>506</v>
       </c>
-      <c r="E2" s="9">
-        <f ca="1">RAND()</f>
-        <v>0.85189760930620362</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A3" s="9">
-        <v>1</v>
-      </c>
-      <c r="B3" s="20" t="s">
+      <c r="D3" s="20" t="s">
         <v>507</v>
       </c>
-      <c r="D3" s="20" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="9">
+        <v>0</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>508</v>
       </c>
-      <c r="E3" s="9">
-        <f ca="1">RAND()</f>
-        <v>4.0850682081250311E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="9">
-        <v>0</v>
-      </c>
-      <c r="B4" s="20" t="s">
+      <c r="D4" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="D4" s="20" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="9">
+        <v>1</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>510</v>
       </c>
-      <c r="E4" s="9">
-        <f t="shared" ref="E4:E20" ca="1" si="0">RAND()</f>
-        <v>0.44790989478392595</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A5" s="9">
-        <v>1</v>
-      </c>
-      <c r="B5" s="20" t="s">
+      <c r="D5" s="20" t="s">
         <v>511</v>
       </c>
-      <c r="D5" s="20" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="9">
+        <v>1</v>
+      </c>
+      <c r="B6" s="25" t="s">
         <v>512</v>
       </c>
-      <c r="E5" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.75126416196341683</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A6" s="9">
-        <v>1</v>
-      </c>
-      <c r="B6" s="25" t="s">
+      <c r="D6" s="20" t="s">
         <v>513</v>
       </c>
-      <c r="D6" s="20" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7" s="9">
+        <v>0</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>515</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>514</v>
       </c>
-      <c r="E6" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.52837041738379686</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A7" s="9">
-        <v>0</v>
-      </c>
-      <c r="B7" s="20" t="s">
+      <c r="D7" s="20" t="s">
         <v>516</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>515</v>
-      </c>
-      <c r="D7" s="20" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8" s="9">
+        <v>0</v>
+      </c>
+      <c r="B8" s="20" t="s">
         <v>517</v>
       </c>
-      <c r="E7" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.16533311701944198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A8" s="9">
-        <v>0</v>
-      </c>
-      <c r="B8" s="20" t="s">
+      <c r="C8" s="20" t="s">
         <v>518</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="D8" s="20" t="s">
         <v>519</v>
       </c>
-      <c r="D8" s="20" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="9">
+        <v>0</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>520</v>
       </c>
-      <c r="E8" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.69897027448398996</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A9" s="9">
-        <v>0</v>
-      </c>
-      <c r="B9" s="20" t="s">
+      <c r="C9" s="20" t="s">
         <v>521</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="D9" s="20" t="s">
         <v>522</v>
       </c>
-      <c r="D9" s="20" t="s">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" s="9">
+        <v>0</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>542</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>543</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A11" s="9">
+        <v>1</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>546</v>
+      </c>
+      <c r="D11" s="20" t="s">
         <v>523</v>
       </c>
-      <c r="E9" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.87539362972776047</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A10" s="9">
-        <v>0</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>543</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>544</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>546</v>
-      </c>
-      <c r="E10" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>2.0416569140482399E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A11" s="9">
-        <v>1</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>547</v>
-      </c>
-      <c r="D11" s="20" t="s">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" s="9">
+        <v>0</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>524</v>
       </c>
-      <c r="E11" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>7.5306413870898425E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A12" s="9">
-        <v>0</v>
-      </c>
-      <c r="B12" s="20" t="s">
+      <c r="D12" s="20" t="s">
         <v>525</v>
       </c>
-      <c r="D12" s="20" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="9">
+        <v>1</v>
+      </c>
+      <c r="B13" s="20" t="s">
         <v>526</v>
       </c>
-      <c r="E12" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.77374420866053051</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A13" s="9">
-        <v>1</v>
-      </c>
-      <c r="B13" s="20" t="s">
+      <c r="D13" s="20" t="s">
         <v>527</v>
       </c>
-      <c r="D13" s="20" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" s="9">
+        <v>1</v>
+      </c>
+      <c r="B14" s="25" t="s">
         <v>528</v>
       </c>
-      <c r="E13" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.96131305137166789</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A14" s="9">
-        <v>1</v>
-      </c>
-      <c r="B14" s="25" t="s">
+      <c r="D14" s="20" t="s">
         <v>529</v>
       </c>
-      <c r="D14" s="20" t="s">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="9">
+        <v>1</v>
+      </c>
+      <c r="B15" s="25" t="s">
         <v>530</v>
       </c>
-      <c r="E14" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.73476379858280649</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A15" s="9">
-        <v>1</v>
-      </c>
-      <c r="B15" s="25" t="s">
+      <c r="D15" s="20" t="s">
         <v>531</v>
       </c>
-      <c r="D15" s="20" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="9">
+        <v>0</v>
+      </c>
+      <c r="B16" s="25" t="s">
         <v>532</v>
       </c>
-      <c r="E15" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.58607073099006635</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A16" s="9">
-        <v>0</v>
-      </c>
-      <c r="B16" s="25" t="s">
+      <c r="C16" s="20" t="s">
         <v>533</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="D16" s="20" t="s">
         <v>534</v>
       </c>
-      <c r="D16" s="20" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="9">
+        <v>0</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="D17" s="20" t="s">
         <v>535</v>
       </c>
-      <c r="E16" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.50983799795056128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" s="9">
-        <v>0</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="D17" s="20" t="s">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" s="9">
+        <v>1</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="D18" s="20" t="s">
         <v>536</v>
       </c>
-      <c r="E17" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.58206928799975566</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="9">
-        <v>1</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="D18" s="20" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" s="9">
+        <v>0</v>
+      </c>
+      <c r="B19" s="20" t="s">
         <v>537</v>
       </c>
-      <c r="E18" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.67652142423217343</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" s="9">
-        <v>0</v>
-      </c>
-      <c r="B19" s="20" t="s">
+      <c r="D19" s="20" t="s">
         <v>538</v>
       </c>
-      <c r="D19" s="20" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" s="9">
+        <v>1</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>540</v>
+      </c>
+      <c r="C20" s="20" t="s">
         <v>539</v>
       </c>
-      <c r="E19" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>9.6958934368195582E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" s="9">
-        <v>1</v>
-      </c>
-      <c r="B20" s="20" t="s">
+      <c r="D20" s="20" t="s">
         <v>541</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>540</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>542</v>
-      </c>
-      <c r="E20" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.25182697229685524</v>
       </c>
     </row>
   </sheetData>
